--- a/data/dividends_info_20260429.xlsx
+++ b/data/dividends_info_20260429.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>43.58000183105469</v>
+        <v>44.72000122070312</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2065167421261255</v>
+        <v>0.2012522306424591</v>
       </c>
       <c r="J2" t="n">
         <v>320</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>55.54999923706055</v>
+        <v>55.95000076293945</v>
       </c>
       <c r="I3" t="n">
-        <v>1.260126029908188</v>
+        <v>1.251117051751089</v>
       </c>
       <c r="J3" t="n">
         <v>299</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.460000038146973</v>
+        <v>9.439999580383301</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6342494689011948</v>
+        <v>0.6355932485916886</v>
       </c>
       <c r="J4" t="n">
         <v>229</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>43.58000183105469</v>
+        <v>44.72000122070312</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2065167421261255</v>
+        <v>0.2012522306424591</v>
       </c>
       <c r="J6" t="n">
         <v>229</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.095000028610229</v>
+        <v>2.079999923706055</v>
       </c>
       <c r="I7" t="n">
-        <v>3.675417610904753</v>
+        <v>3.701923212708811</v>
       </c>
       <c r="J7" t="n">
         <v>208</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5.96999979019165</v>
+        <v>5.869999885559082</v>
       </c>
       <c r="I8" t="n">
-        <v>3.350083869828403</v>
+        <v>3.407155091979209</v>
       </c>
       <c r="J8" t="n">
         <v>201</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5.900000095367432</v>
+        <v>6.050000190734863</v>
       </c>
       <c r="I9" t="n">
-        <v>1.016949136104436</v>
+        <v>0.9917355059242088</v>
       </c>
       <c r="J9" t="n">
         <v>173</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>4.940000057220459</v>
+        <v>4.949999809265137</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7692307603207009</v>
+        <v>0.7676767972571169</v>
       </c>
       <c r="J11" t="n">
         <v>152</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>43.58000183105469</v>
+        <v>44.72000122070312</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2065167421261255</v>
+        <v>0.2012522306424591</v>
       </c>
       <c r="J12" t="n">
         <v>145</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>4.940000057220459</v>
+        <v>4.949999809265137</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7692307603207009</v>
+        <v>0.7676767972571169</v>
       </c>
       <c r="J14" t="n">
         <v>96</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>6.070000171661377</v>
+        <v>6.079999923706055</v>
       </c>
       <c r="I15" t="n">
-        <v>4.118616028499622</v>
+        <v>4.111842156859978</v>
       </c>
       <c r="J15" t="n">
         <v>89</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>9.800999641418457</v>
+        <v>9.668000221252441</v>
       </c>
       <c r="I16" t="n">
-        <v>2.652790628633992</v>
+        <v>2.689284175112672</v>
       </c>
       <c r="J16" t="n">
         <v>82</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>16.20000076293945</v>
+        <v>16.04000091552734</v>
       </c>
       <c r="I17" t="n">
-        <v>3.703703529277682</v>
+        <v>3.740648165544533</v>
       </c>
       <c r="J17" t="n">
         <v>82</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>3.74399995803833</v>
+        <v>3.736000061035156</v>
       </c>
       <c r="I18" t="n">
-        <v>5.876068441925653</v>
+        <v>5.888650867394345</v>
       </c>
       <c r="J18" t="n">
         <v>82</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>5.900000095367432</v>
+        <v>5.789999961853027</v>
       </c>
       <c r="I20" t="n">
-        <v>4.067796544417744</v>
+        <v>4.145077747516781</v>
       </c>
       <c r="J20" t="n">
         <v>82</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>5.46999979019165</v>
+        <v>5.389999866485596</v>
       </c>
       <c r="I22" t="n">
-        <v>2.193784362024548</v>
+        <v>2.226345138636205</v>
       </c>
       <c r="J22" t="n">
         <v>75</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>4.369999885559082</v>
+        <v>4.099999904632568</v>
       </c>
       <c r="I25" t="n">
-        <v>1.601830705564068</v>
+        <v>1.707317112883524</v>
       </c>
       <c r="J25" t="n">
         <v>68</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>34.79999923706055</v>
+        <v>34.29999923706055</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4310344922084259</v>
+        <v>0.4373177939838775</v>
       </c>
       <c r="J26" t="n">
         <v>68</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>6</v>
+        <v>5.800000190734863</v>
       </c>
       <c r="I27" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.6896551497342619</v>
       </c>
       <c r="J27" t="n">
         <v>61</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>22.63999938964844</v>
+        <v>22.18000030517578</v>
       </c>
       <c r="I28" t="n">
-        <v>4.196113187327925</v>
+        <v>4.283137903196124</v>
       </c>
       <c r="J28" t="n">
         <v>54</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>25.5</v>
+        <v>25.60000038146973</v>
       </c>
       <c r="I29" t="n">
-        <v>0.7647058823529412</v>
+        <v>0.7617187386495063</v>
       </c>
       <c r="J29" t="n">
         <v>54</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>4.938000202178955</v>
+        <v>4.912000179290771</v>
       </c>
       <c r="I31" t="n">
-        <v>5.872822764811427</v>
+        <v>5.903908579292279</v>
       </c>
       <c r="J31" t="n">
         <v>54</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>4.050000190734863</v>
+        <v>3.953999996185303</v>
       </c>
       <c r="I32" t="n">
-        <v>3.950617097896195</v>
+        <v>4.046535158178125</v>
       </c>
       <c r="J32" t="n">
         <v>54</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>2.601999998092651</v>
+        <v>2.562000036239624</v>
       </c>
       <c r="I33" t="n">
-        <v>5.326671794834673</v>
+        <v>5.409835989051357</v>
       </c>
       <c r="J33" t="n">
         <v>54</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>52.36000061035156</v>
+        <v>52.13999938964844</v>
       </c>
       <c r="I34" t="n">
-        <v>1.203208542124137</v>
+        <v>1.208285399644781</v>
       </c>
       <c r="J34" t="n">
         <v>54</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>5.099999904632568</v>
+        <v>5.045000076293945</v>
       </c>
       <c r="I35" t="n">
-        <v>2.745098090547638</v>
+        <v>2.775024735041113</v>
       </c>
       <c r="J35" t="n">
         <v>54</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>19.20000076293945</v>
+        <v>19.39999961853027</v>
       </c>
       <c r="I36" t="n">
-        <v>4.06249983857076</v>
+        <v>4.020618635760015</v>
       </c>
       <c r="J36" t="n">
         <v>54</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>22.3700008392334</v>
+        <v>22.45000076293945</v>
       </c>
       <c r="I37" t="n">
-        <v>3.799731641087988</v>
+        <v>3.786191408078628</v>
       </c>
       <c r="J37" t="n">
         <v>54</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>43.58000183105469</v>
+        <v>44.72000122070312</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2065167421261255</v>
+        <v>0.2012522306424591</v>
       </c>
       <c r="J38" t="n">
         <v>54</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>6.638000011444092</v>
+        <v>6.611999988555908</v>
       </c>
       <c r="I39" t="n">
-        <v>2.731244345999305</v>
+        <v>2.741984275768227</v>
       </c>
       <c r="J39" t="n">
         <v>54</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>8.460000038146973</v>
+        <v>8.430000305175781</v>
       </c>
       <c r="I40" t="n">
-        <v>3.073286038151707</v>
+        <v>3.084222901396188</v>
       </c>
       <c r="J40" t="n">
         <v>54</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>10.10999965667725</v>
+        <v>10.06999969482422</v>
       </c>
       <c r="I41" t="n">
-        <v>2.739861616286532</v>
+        <v>2.750744869857072</v>
       </c>
       <c r="J41" t="n">
         <v>54</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1.144999980926514</v>
+        <v>1.174999952316284</v>
       </c>
       <c r="I42" t="n">
-        <v>1.179039320950559</v>
+        <v>1.148936216838764</v>
       </c>
       <c r="J42" t="n">
         <v>47</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>4.228000164031982</v>
+        <v>4.208000183105469</v>
       </c>
       <c r="I43" t="n">
-        <v>2.601702831891563</v>
+        <v>2.614068327316966</v>
       </c>
       <c r="J43" t="n">
         <v>47</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>3.430000066757202</v>
+        <v>3.400000095367432</v>
       </c>
       <c r="I45" t="n">
-        <v>4.664722941281676</v>
+        <v>4.705882220944735</v>
       </c>
       <c r="J45" t="n">
         <v>40</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>28</v>
+        <v>27.64999961853027</v>
       </c>
       <c r="I47" t="n">
-        <v>3.964285714285714</v>
+        <v>4.014466601497197</v>
       </c>
       <c r="J47" t="n">
         <v>36</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>0.9029999971389771</v>
+        <v>0.8999999761581421</v>
       </c>
       <c r="I48" t="n">
-        <v>3.322259146738714</v>
+        <v>3.333333421636513</v>
       </c>
       <c r="J48" t="n">
         <v>33</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>0.5090000033378601</v>
+        <v>0.5099999904632568</v>
       </c>
       <c r="I49" t="n">
-        <v>4.518664017519315</v>
+        <v>4.509804005899691</v>
       </c>
       <c r="J49" t="n">
         <v>33</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>9.180000305175781</v>
+        <v>9.159999847412109</v>
       </c>
       <c r="I51" t="n">
-        <v>2.178649165046736</v>
+        <v>2.183406149908443</v>
       </c>
       <c r="J51" t="n">
         <v>33</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>2.559999942779541</v>
+        <v>2.519999980926514</v>
       </c>
       <c r="I52" t="n">
-        <v>7.031250157160687</v>
+        <v>7.142857196920313</v>
       </c>
       <c r="J52" t="n">
         <v>26</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>8.649999618530273</v>
+        <v>8.800000190734863</v>
       </c>
       <c r="I53" t="n">
-        <v>3.468208245435428</v>
+        <v>3.409090835200855</v>
       </c>
       <c r="J53" t="n">
         <v>26</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>13.10000038146973</v>
+        <v>13.0600004196167</v>
       </c>
       <c r="I54" t="n">
-        <v>1.908396890992699</v>
+        <v>1.914241898679336</v>
       </c>
       <c r="J54" t="n">
         <v>26</v>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>3.299999952316284</v>
+        <v>3.349999904632568</v>
       </c>
       <c r="I55" t="n">
-        <v>0.909090922226919</v>
+        <v>0.8955224135533352</v>
       </c>
       <c r="J55" t="n">
         <v>26</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>3.819999933242798</v>
+        <v>3.769999980926514</v>
       </c>
       <c r="I56" t="n">
-        <v>3.926701639302517</v>
+        <v>3.978779860978569</v>
       </c>
       <c r="J56" t="n">
         <v>26</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>2.378999948501587</v>
+        <v>2.342000007629395</v>
       </c>
       <c r="I58" t="n">
-        <v>4.371584794085615</v>
+        <v>4.440649003467351</v>
       </c>
       <c r="J58" t="n">
         <v>19</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>9.609999656677246</v>
+        <v>9.430000305175781</v>
       </c>
       <c r="I59" t="n">
-        <v>3.017690014156258</v>
+        <v>3.075291522958166</v>
       </c>
       <c r="J59" t="n">
         <v>19</v>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>2.095000028610229</v>
+        <v>2.079999923706055</v>
       </c>
       <c r="I60" t="n">
-        <v>3.675417610904753</v>
+        <v>3.701923212708811</v>
       </c>
       <c r="J60" t="n">
         <v>19</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>37.84000015258789</v>
+        <v>37.90999984741211</v>
       </c>
       <c r="I61" t="n">
-        <v>4.334038037491498</v>
+        <v>4.326035364286484</v>
       </c>
       <c r="J61" t="n">
         <v>19</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>36.47999954223633</v>
+        <v>36.0099983215332</v>
       </c>
       <c r="I62" t="n">
-        <v>5.482456209146636</v>
+        <v>5.554013033108205</v>
       </c>
       <c r="J62" t="n">
         <v>19</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>3.910000085830688</v>
+        <v>3.931999921798706</v>
       </c>
       <c r="I63" t="n">
-        <v>2.557544700891094</v>
+        <v>2.543235045494474</v>
       </c>
       <c r="J63" t="n">
         <v>19</v>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>30.67000007629395</v>
+        <v>30.76000022888184</v>
       </c>
       <c r="I64" t="n">
-        <v>0.4840560796566499</v>
+        <v>0.4826397883463108</v>
       </c>
       <c r="J64" t="n">
         <v>19</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>23.10000038146973</v>
+        <v>23.13999938964844</v>
       </c>
       <c r="I65" t="n">
-        <v>3.982683916914574</v>
+        <v>3.975799586285025</v>
       </c>
       <c r="J65" t="n">
         <v>19</v>
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>8.069999694824219</v>
+        <v>8.050000190734863</v>
       </c>
       <c r="I66" t="n">
-        <v>3.717472259539343</v>
+        <v>3.726707986234393</v>
       </c>
       <c r="J66" t="n">
         <v>19</v>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>81.59999847412109</v>
+        <v>81.37999725341797</v>
       </c>
       <c r="I67" t="n">
-        <v>1.274509827754261</v>
+        <v>1.277955314696597</v>
       </c>
       <c r="J67" t="n">
         <v>19</v>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>46.38000106811523</v>
+        <v>46.20999908447266</v>
       </c>
       <c r="I68" t="n">
-        <v>1.509271202844425</v>
+        <v>1.51482366126082</v>
       </c>
       <c r="J68" t="n">
         <v>19</v>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>55.59999847412109</v>
+        <v>55.95000076293945</v>
       </c>
       <c r="I69" t="n">
-        <v>3.956834640964937</v>
+        <v>3.93208216264628</v>
       </c>
       <c r="J69" t="n">
         <v>19</v>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>9.059000015258789</v>
+        <v>9.071999549865723</v>
       </c>
       <c r="I70" t="n">
-        <v>9.493321542680585</v>
+        <v>9.479718283415579</v>
       </c>
       <c r="J70" t="n">
         <v>19</v>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>12.35000038146973</v>
+        <v>12.41399955749512</v>
       </c>
       <c r="I71" t="n">
-        <v>4.534412815405569</v>
+        <v>4.511036087977727</v>
       </c>
       <c r="J71" t="n">
         <v>19</v>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>9.590000152587891</v>
+        <v>9.680000305175781</v>
       </c>
       <c r="I73" t="n">
-        <v>3.128258552936979</v>
+        <v>3.099173456013153</v>
       </c>
       <c r="J73" t="n">
         <v>19</v>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>2.230000019073486</v>
+        <v>2.220000028610229</v>
       </c>
       <c r="I74" t="n">
-        <v>4.843049285931015</v>
+        <v>4.864864802168965</v>
       </c>
       <c r="J74" t="n">
         <v>19</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>73.80000305175781</v>
+        <v>74.69999694824219</v>
       </c>
       <c r="I75" t="n">
-        <v>2.791327797852894</v>
+        <v>2.757697569154285</v>
       </c>
       <c r="J75" t="n">
         <v>19</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>15.11999988555908</v>
+        <v>15.14000034332275</v>
       </c>
       <c r="I76" t="n">
-        <v>4.960317497861329</v>
+        <v>4.95376474896036</v>
       </c>
       <c r="J76" t="n">
         <v>19</v>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>15.28999996185303</v>
+        <v>15.23999977111816</v>
       </c>
       <c r="I77" t="n">
-        <v>1.962066715163303</v>
+        <v>1.968503966571837</v>
       </c>
       <c r="J77" t="n">
         <v>19</v>
@@ -4095,10 +4095,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>46</v>
+        <v>45.40000152587891</v>
       </c>
       <c r="I78" t="n">
-        <v>1.847826086956522</v>
+        <v>1.872246633109655</v>
       </c>
       <c r="J78" t="n">
         <v>19</v>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>33.45999908447266</v>
+        <v>33.65999984741211</v>
       </c>
       <c r="I79" t="n">
-        <v>2.540346752114671</v>
+        <v>2.525252536700028</v>
       </c>
       <c r="J79" t="n">
         <v>19</v>
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>57.36000061035156</v>
+        <v>56.93999862670898</v>
       </c>
       <c r="I80" t="n">
-        <v>2.266387702522781</v>
+        <v>2.283105077895463</v>
       </c>
       <c r="J80" t="n">
         <v>19</v>
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>8.140000343322754</v>
+        <v>8.119999885559082</v>
       </c>
       <c r="I81" t="n">
-        <v>7.371007060118619</v>
+        <v>7.389162665717064</v>
       </c>
       <c r="J81" t="n">
         <v>19</v>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>6.150000095367432</v>
+        <v>5.949999809265137</v>
       </c>
       <c r="I82" t="n">
-        <v>7.642276304256217</v>
+        <v>7.899159917083225</v>
       </c>
       <c r="J82" t="n">
         <v>19</v>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>5.96999979019165</v>
+        <v>5.869999885559082</v>
       </c>
       <c r="I83" t="n">
-        <v>3.350083869828403</v>
+        <v>3.407155091979209</v>
       </c>
       <c r="J83" t="n">
         <v>19</v>
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>22.76000022888184</v>
+        <v>22.47999954223633</v>
       </c>
       <c r="I84" t="n">
-        <v>4.393673066536381</v>
+        <v>4.448398667095876</v>
       </c>
       <c r="J84" t="n">
         <v>19</v>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>23.55999946594238</v>
+        <v>23.64500045776367</v>
       </c>
       <c r="I86" t="n">
-        <v>1.146010212734953</v>
+        <v>1.141890440993193</v>
       </c>
       <c r="J86" t="n">
         <v>19</v>
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>8.479999542236328</v>
+        <v>8.399999618530273</v>
       </c>
       <c r="I87" t="n">
-        <v>2.358490693352755</v>
+        <v>2.380952489078726</v>
       </c>
       <c r="J87" t="n">
         <v>19</v>
@@ -4565,10 +4565,10 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>9.305000305175781</v>
+        <v>9.239999771118164</v>
       </c>
       <c r="I88" t="n">
-        <v>2.579258378599979</v>
+        <v>2.597402661742239</v>
       </c>
       <c r="J88" t="n">
         <v>19</v>
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>5.900000095367432</v>
+        <v>6.050000190734863</v>
       </c>
       <c r="I91" t="n">
-        <v>1.016949136104436</v>
+        <v>0.9917355059242088</v>
       </c>
       <c r="J91" t="n">
         <v>19</v>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>35.84000015258789</v>
+        <v>35.90000152587891</v>
       </c>
       <c r="I92" t="n">
-        <v>0.9765624958423098</v>
+        <v>0.9749303206789522</v>
       </c>
       <c r="J92" t="n">
         <v>19</v>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>7.21999979019165</v>
+        <v>7.164999961853027</v>
       </c>
       <c r="I93" t="n">
-        <v>7.677285541656317</v>
+        <v>7.736217766240514</v>
       </c>
       <c r="J93" t="n">
         <v>19</v>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>2.269999980926514</v>
+        <v>2.230000019073486</v>
       </c>
       <c r="I94" t="n">
-        <v>2.643171828376432</v>
+        <v>2.690582936628342</v>
       </c>
       <c r="J94" t="n">
         <v>19</v>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>6.050000190734863</v>
+        <v>6.019999980926514</v>
       </c>
       <c r="I96" t="n">
-        <v>1.702479285169892</v>
+        <v>1.710963460570438</v>
       </c>
       <c r="J96" t="n">
         <v>19</v>
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>5.72599983215332</v>
+        <v>5.722000122070312</v>
       </c>
       <c r="I97" t="n">
-        <v>3.3181977919924</v>
+        <v>3.320517230804513</v>
       </c>
       <c r="J97" t="n">
         <v>19</v>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>10.21000003814697</v>
+        <v>10.14500045776367</v>
       </c>
       <c r="I98" t="n">
-        <v>4.231145919548932</v>
+        <v>4.258255106035042</v>
       </c>
       <c r="J98" t="n">
         <v>19</v>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>24.96999931335449</v>
+        <v>25.09000015258789</v>
       </c>
       <c r="I99" t="n">
-        <v>1.762114585901004</v>
+        <v>1.753686717114733</v>
       </c>
       <c r="J99" t="n">
         <v>19</v>
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>8.529999732971191</v>
+        <v>8.560000419616699</v>
       </c>
       <c r="I101" t="n">
-        <v>5.509965002499341</v>
+        <v>5.490653936452093</v>
       </c>
       <c r="J101" t="n">
         <v>19</v>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>52.20000076293945</v>
+        <v>52.29999923706055</v>
       </c>
       <c r="I102" t="n">
-        <v>2.68199229796556</v>
+        <v>2.676864283791307</v>
       </c>
       <c r="J102" t="n">
         <v>19</v>
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>4.113999843597412</v>
+        <v>3.967999935150146</v>
       </c>
       <c r="I103" t="n">
-        <v>7.292173344801843</v>
+        <v>7.560483994530312</v>
       </c>
       <c r="J103" t="n">
         <v>19</v>
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>11.94999980926514</v>
+        <v>11.89999961853027</v>
       </c>
       <c r="I104" t="n">
-        <v>1.004184116446269</v>
+        <v>1.008403393670199</v>
       </c>
       <c r="J104" t="n">
         <v>19</v>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>3.539999961853027</v>
+        <v>3.480000019073486</v>
       </c>
       <c r="I105" t="n">
-        <v>4.802259938754712</v>
+        <v>4.885057444489921</v>
       </c>
       <c r="J105" t="n">
         <v>19</v>
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>20.75</v>
+        <v>20.20000076293945</v>
       </c>
       <c r="I106" t="n">
-        <v>3.373493975903615</v>
+        <v>3.465346403769827</v>
       </c>
       <c r="J106" t="n">
         <v>19</v>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>6.139999866485596</v>
+        <v>6.070000171661377</v>
       </c>
       <c r="I108" t="n">
-        <v>5.374592950746838</v>
+        <v>5.4365731576195</v>
       </c>
       <c r="J108" t="n">
         <v>19</v>
@@ -5599,10 +5599,10 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>49.5</v>
+        <v>49.13999938964844</v>
       </c>
       <c r="I110" t="n">
-        <v>1.434343434343434</v>
+        <v>1.444851462797463</v>
       </c>
       <c r="J110" t="n">
         <v>19</v>
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>92.44999694824219</v>
+        <v>93.90000152587891</v>
       </c>
       <c r="I111" t="n">
-        <v>1.460248831328564</v>
+        <v>1.437699657148503</v>
       </c>
       <c r="J111" t="n">
         <v>19</v>
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>7.199999809265137</v>
+        <v>7.179999828338623</v>
       </c>
       <c r="I112" t="n">
-        <v>1.111111140545505</v>
+        <v>1.114206154772446</v>
       </c>
       <c r="J112" t="n">
         <v>19</v>
@@ -5787,10 +5787,10 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>4.738999843597412</v>
+        <v>4.532999992370605</v>
       </c>
       <c r="I114" t="n">
-        <v>3.587254813474559</v>
+        <v>3.750275761882271</v>
       </c>
       <c r="J114" t="n">
         <v>19</v>
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>58.29999923706055</v>
+        <v>59.20000076293945</v>
       </c>
       <c r="I116" t="n">
-        <v>0.771869649895194</v>
+        <v>0.7601351253389008</v>
       </c>
       <c r="J116" t="n">
         <v>19</v>
@@ -5928,10 +5928,10 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>4.71999979019165</v>
+        <v>4.690000057220459</v>
       </c>
       <c r="I117" t="n">
-        <v>0.8474576647889183</v>
+        <v>0.8528784544131991</v>
       </c>
       <c r="J117" t="n">
         <v>19</v>
@@ -5975,10 +5975,10 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>33.47999954223633</v>
+        <v>33.04000091552734</v>
       </c>
       <c r="I118" t="n">
-        <v>3.136200759726367</v>
+        <v>3.177966013634541</v>
       </c>
       <c r="J118" t="n">
         <v>19</v>
@@ -6069,10 +6069,10 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>20.47999954223633</v>
+        <v>20.28000068664551</v>
       </c>
       <c r="I120" t="n">
-        <v>1.85546879147296</v>
+        <v>1.873767194940146</v>
       </c>
       <c r="J120" t="n">
         <v>19</v>
@@ -6116,10 +6116,10 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>27.17000007629395</v>
+        <v>26.97999954223633</v>
       </c>
       <c r="I121" t="n">
-        <v>2.208317991590678</v>
+        <v>2.223869570719299</v>
       </c>
       <c r="J121" t="n">
         <v>19</v>
@@ -6163,10 +6163,10 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>33.70000076293945</v>
+        <v>33.54999923706055</v>
       </c>
       <c r="I122" t="n">
-        <v>1.038575644143313</v>
+        <v>1.043219099729151</v>
       </c>
       <c r="J122" t="n">
         <v>19</v>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>2.855000019073486</v>
+        <v>2.805000066757202</v>
       </c>
       <c r="I124" t="n">
-        <v>0.3502626946827563</v>
+        <v>0.3565062303745603</v>
       </c>
       <c r="J124" t="n">
         <v>19</v>
@@ -6304,10 +6304,10 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>22.03000068664551</v>
+        <v>22.13999938964844</v>
       </c>
       <c r="I125" t="n">
-        <v>5.083976237363167</v>
+        <v>5.058717393297022</v>
       </c>
       <c r="J125" t="n">
         <v>19</v>
@@ -6351,10 +6351,10 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>1.419999957084656</v>
+        <v>1.509999990463257</v>
       </c>
       <c r="I126" t="n">
-        <v>7.042253733958271</v>
+        <v>6.622516598117379</v>
       </c>
       <c r="J126" t="n">
         <v>19</v>
@@ -6398,10 +6398,10 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>2.499000072479248</v>
+        <v>2.522000074386597</v>
       </c>
       <c r="I127" t="n">
-        <v>10.40416136291085</v>
+        <v>10.30927804644246</v>
       </c>
       <c r="J127" t="n">
         <v>19</v>
@@ -6445,10 +6445,10 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>2.065999984741211</v>
+        <v>2.108000040054321</v>
       </c>
       <c r="I128" t="n">
-        <v>4.467570216926288</v>
+        <v>4.378557791565388</v>
       </c>
       <c r="J128" t="n">
         <v>19</v>
@@ -6492,10 +6492,10 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>9.359999656677246</v>
+        <v>9.319999694824219</v>
       </c>
       <c r="I129" t="n">
-        <v>3.739316376473546</v>
+        <v>3.755364929833307</v>
       </c>
       <c r="J129" t="n">
         <v>12</v>
@@ -6539,10 +6539,10 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>5.199999809265137</v>
+        <v>5.150000095367432</v>
       </c>
       <c r="I130" t="n">
-        <v>1.846153913870368</v>
+        <v>1.86407763538402</v>
       </c>
       <c r="J130" t="n">
         <v>12</v>
@@ -6586,10 +6586,10 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>6.25</v>
+        <v>6.199999809265137</v>
       </c>
       <c r="I131" t="n">
-        <v>4.8</v>
+        <v>4.838709826275912</v>
       </c>
       <c r="J131" t="n">
         <v>12</v>
@@ -6680,10 +6680,10 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>9.460000038146973</v>
+        <v>9.439999580383301</v>
       </c>
       <c r="I133" t="n">
-        <v>0.6342494689011948</v>
+        <v>0.6355932485916886</v>
       </c>
       <c r="J133" t="n">
         <v>12</v>
@@ -6727,10 +6727,10 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>19.89999961853027</v>
+        <v>19.52000045776367</v>
       </c>
       <c r="I134" t="n">
-        <v>2.512562862234506</v>
+        <v>2.561475349766887</v>
       </c>
       <c r="J134" t="n">
         <v>12</v>
@@ -6774,10 +6774,10 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>2.220000028610229</v>
+        <v>2.200000047683716</v>
       </c>
       <c r="I135" t="n">
-        <v>2.702702667871647</v>
+        <v>2.727272668160684</v>
       </c>
       <c r="J135" t="n">
         <v>12</v>
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>16.36000061035156</v>
+        <v>16.1200008392334</v>
       </c>
       <c r="I136" t="n">
-        <v>3.056234604805772</v>
+        <v>3.101736811223256</v>
       </c>
       <c r="J136" t="n">
         <v>12</v>
@@ -6915,10 +6915,10 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>3.529999971389771</v>
+        <v>3.569999933242798</v>
       </c>
       <c r="I138" t="n">
-        <v>3.116147334037873</v>
+        <v>3.081232550614696</v>
       </c>
       <c r="J138" t="n">
         <v>12</v>
@@ -6962,10 +6962,10 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>9.399999618530273</v>
+        <v>9.199999809265137</v>
       </c>
       <c r="I139" t="n">
-        <v>0.9042553558453239</v>
+        <v>0.923913062632873</v>
       </c>
       <c r="J139" t="n">
         <v>12</v>
@@ -7009,10 +7009,10 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>4.880000114440918</v>
+        <v>4.929999828338623</v>
       </c>
       <c r="I140" t="n">
-        <v>1.946721265822835</v>
+        <v>1.926977754723662</v>
       </c>
       <c r="J140" t="n">
         <v>12</v>
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>1.259999990463257</v>
+        <v>1.220000028610229</v>
       </c>
       <c r="I141" t="n">
-        <v>2.380952398973438</v>
+        <v>2.459016335776212</v>
       </c>
       <c r="J141" t="n">
         <v>12</v>
@@ -7197,10 +7197,10 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>7.019999980926514</v>
+        <v>6.989999771118164</v>
       </c>
       <c r="I144" t="n">
-        <v>3.133903142418014</v>
+        <v>3.147353465003153</v>
       </c>
       <c r="J144" t="n">
         <v>12</v>
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>27.875</v>
+        <v>28.14999961853027</v>
       </c>
       <c r="I145" t="n">
-        <v>2.188340807174888</v>
+        <v>2.166962729187591</v>
       </c>
       <c r="J145" t="n">
         <v>5</v>
@@ -7291,10 +7291,10 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>3.039999961853027</v>
+        <v>3.089999914169312</v>
       </c>
       <c r="I146" t="n">
-        <v>4.934210588231972</v>
+        <v>4.854369066878265</v>
       </c>
       <c r="J146" t="n">
         <v>5</v>
@@ -7338,10 +7338,10 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>12.14999961853027</v>
+        <v>11.94999980926514</v>
       </c>
       <c r="I147" t="n">
-        <v>5.761317053314242</v>
+        <v>5.857740679269905</v>
       </c>
       <c r="J147" t="n">
         <v>5</v>
@@ -7385,10 +7385,10 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>9.199999809265137</v>
+        <v>9.159999847412109</v>
       </c>
       <c r="I148" t="n">
-        <v>5.548913158518608</v>
+        <v>5.573144197641301</v>
       </c>
       <c r="J148" t="n">
         <v>5</v>
@@ -7432,10 +7432,10 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>7.965000152587891</v>
+        <v>7.914999961853027</v>
       </c>
       <c r="I149" t="n">
-        <v>3.389830443534579</v>
+        <v>3.411244488961295</v>
       </c>
       <c r="J149" t="n">
         <v>5</v>
@@ -7479,10 +7479,10 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>5.735000133514404</v>
+        <v>5.800000190734863</v>
       </c>
       <c r="I150" t="n">
-        <v>6.102876928540195</v>
+        <v>6.034482560174792</v>
       </c>
       <c r="J150" t="n">
         <v>5</v>
@@ -7573,10 +7573,10 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>19.04999923706055</v>
+        <v>19</v>
       </c>
       <c r="I152" t="n">
-        <v>3.937008031690223</v>
+        <v>3.947368421052631</v>
       </c>
       <c r="J152" t="n">
         <v>5</v>
@@ -7620,10 +7620,10 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>11.60000038146973</v>
+        <v>11.80000019073486</v>
       </c>
       <c r="I153" t="n">
-        <v>3.706896429821658</v>
+        <v>3.644067737707562</v>
       </c>
       <c r="J153" t="n">
         <v>5</v>
@@ -7667,10 +7667,10 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>4.235000133514404</v>
+        <v>4.239999771118164</v>
       </c>
       <c r="I154" t="n">
-        <v>3.541912521157889</v>
+        <v>3.537736040029132</v>
       </c>
       <c r="J154" t="n">
         <v>5</v>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>12.53999996185303</v>
+        <v>12.34000015258789</v>
       </c>
       <c r="I155" t="n">
-        <v>1.572320578945715</v>
+        <v>1.597803870031967</v>
       </c>
       <c r="J155" t="n">
         <v>5</v>
@@ -7761,10 +7761,10 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>29.14999961853027</v>
+        <v>29.25</v>
       </c>
       <c r="I156" t="n">
-        <v>3.773584955043171</v>
+        <v>3.760683760683761</v>
       </c>
       <c r="J156" t="n">
         <v>5</v>
@@ -7808,10 +7808,10 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>46.29999923706055</v>
+        <v>53.09999847412109</v>
       </c>
       <c r="I157" t="n">
-        <v>1.015118807224064</v>
+        <v>0.8851224359809726</v>
       </c>
       <c r="J157" t="n">
         <v>5</v>
@@ -7855,10 +7855,10 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>78.90000152587891</v>
+        <v>78.09999847412109</v>
       </c>
       <c r="I158" t="n">
-        <v>1.520912518114977</v>
+        <v>1.536491707355958</v>
       </c>
       <c r="J158" t="n">
         <v>5</v>
@@ -7902,10 +7902,10 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>24.54999923706055</v>
+        <v>25</v>
       </c>
       <c r="I159" t="n">
-        <v>1.099796368190552</v>
+        <v>1.08</v>
       </c>
       <c r="J159" t="n">
         <v>5</v>
@@ -7949,10 +7949,10 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>10.55000019073486</v>
+        <v>10.35000038146973</v>
       </c>
       <c r="I160" t="n">
-        <v>3.601895669478002</v>
+        <v>3.671497449220761</v>
       </c>
       <c r="J160" t="n">
         <v>5</v>
@@ -7996,10 +7996,10 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>29.5</v>
+        <v>30</v>
       </c>
       <c r="I161" t="n">
-        <v>1.016949152542373</v>
+        <v>1</v>
       </c>
       <c r="J161" t="n">
         <v>5</v>
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>0.1842000037431717</v>
+        <v>0.1790000051259995</v>
       </c>
       <c r="I162" t="n">
-        <v>3.800217078040907</v>
+        <v>3.910614413151915</v>
       </c>
       <c r="J162" t="n">
         <v>-2</v>
@@ -8090,10 +8090,10 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>7.03000020980835</v>
+        <v>7</v>
       </c>
       <c r="I163" t="n">
-        <v>2.275960102771631</v>
+        <v>2.285714285714286</v>
       </c>
       <c r="J163" t="n">
         <v>-2</v>
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>2.180000066757202</v>
+        <v>2.190000057220459</v>
       </c>
       <c r="I164" t="n">
-        <v>2.981651284840964</v>
+        <v>2.968036452131321</v>
       </c>
       <c r="J164" t="n">
         <v>-2</v>
@@ -8184,10 +8184,10 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>7.579999923706055</v>
+        <v>7.53000020980835</v>
       </c>
       <c r="I165" t="n">
-        <v>3.298153067497244</v>
+        <v>3.320053028343314</v>
       </c>
       <c r="J165" t="n">
         <v>-2</v>
@@ -8231,10 +8231,10 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>1.419999957084656</v>
+        <v>1.389999985694885</v>
       </c>
       <c r="I166" t="n">
-        <v>4.929577613770789</v>
+        <v>5.035971274849027</v>
       </c>
       <c r="J166" t="n">
         <v>-2</v>
@@ -8278,10 +8278,10 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>6.570000171661377</v>
+        <v>6.579999923706055</v>
       </c>
       <c r="I167" t="n">
-        <v>7.610349877259797</v>
+        <v>7.598784282635446</v>
       </c>
       <c r="J167" t="n">
         <v>-9</v>
@@ -8325,10 +8325,10 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>18.79000091552734</v>
+        <v>18.70999908447266</v>
       </c>
       <c r="I168" t="n">
-        <v>3.459286686159044</v>
+        <v>3.474078203132741</v>
       </c>
       <c r="J168" t="n">
         <v>-9</v>
@@ -8419,10 +8419,10 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>6.179999828338623</v>
+        <v>6.157999992370605</v>
       </c>
       <c r="I170" t="n">
-        <v>1.618123022292755</v>
+        <v>1.623903866903118</v>
       </c>
       <c r="J170" t="n">
         <v>-9</v>
@@ -8466,10 +8466,10 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>9.239999771118164</v>
+        <v>8.979999542236328</v>
       </c>
       <c r="I171" t="n">
-        <v>1.731601774494826</v>
+        <v>1.781737284589599</v>
       </c>
       <c r="J171" t="n">
         <v>-9</v>
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>287.8999938964844</v>
+        <v>290.25</v>
       </c>
       <c r="I172" t="n">
-        <v>1.255644347564588</v>
+        <v>1.245478036175711</v>
       </c>
       <c r="J172" t="n">
         <v>-9</v>
@@ -8560,10 +8560,10 @@
         </is>
       </c>
       <c r="H173" t="n">
-        <v>30.20000076293945</v>
+        <v>30</v>
       </c>
       <c r="I173" t="n">
-        <v>4.503311144511466</v>
+        <v>4.533333333333333</v>
       </c>
       <c r="J173" t="n">
         <v>-9</v>
@@ -8607,10 +8607,10 @@
         </is>
       </c>
       <c r="H174" t="n">
-        <v>13.98999977111816</v>
+        <v>13.97999954223633</v>
       </c>
       <c r="I174" t="n">
-        <v>41.61258109537984</v>
+        <v>41.64234757241444</v>
       </c>
       <c r="J174" t="n">
         <v>-9</v>
@@ -8654,10 +8654,10 @@
         </is>
       </c>
       <c r="H175" t="n">
-        <v>14.69999980926514</v>
+        <v>16.52000045776367</v>
       </c>
       <c r="I175" t="n">
-        <v>3.979591888370538</v>
+        <v>3.541162129478487</v>
       </c>
       <c r="J175" t="n">
         <v>-9</v>
@@ -8701,10 +8701,10 @@
         </is>
       </c>
       <c r="H176" t="n">
-        <v>19.79500007629395</v>
+        <v>19.71500015258789</v>
       </c>
       <c r="I176" t="n">
-        <v>3.182621861944189</v>
+        <v>3.195536368876482</v>
       </c>
       <c r="J176" t="n">
         <v>-9</v>
@@ -8748,10 +8748,10 @@
         </is>
       </c>
       <c r="H177" t="n">
-        <v>124.3000030517578</v>
+        <v>124.3499984741211</v>
       </c>
       <c r="I177" t="n">
-        <v>0.7240546885789256</v>
+        <v>0.723763579448135</v>
       </c>
       <c r="J177" t="n">
         <v>-9</v>
@@ -8795,10 +8795,10 @@
         </is>
       </c>
       <c r="H178" t="n">
-        <v>65.37000274658203</v>
+        <v>65.73000335693359</v>
       </c>
       <c r="I178" t="n">
-        <v>2.63240007296768</v>
+        <v>2.617982522616865</v>
       </c>
       <c r="J178" t="n">
         <v>-9</v>
@@ -8842,10 +8842,10 @@
         </is>
       </c>
       <c r="H179" t="n">
-        <v>25.70000076293945</v>
+        <v>26.20000076293945</v>
       </c>
       <c r="I179" t="n">
-        <v>0.5447470655405048</v>
+        <v>0.5343511294779558</v>
       </c>
       <c r="J179" t="n">
         <v>-16</v>
@@ -8936,10 +8936,10 @@
         </is>
       </c>
       <c r="H181" t="n">
-        <v>2.200000047683716</v>
+        <v>2.160000085830688</v>
       </c>
       <c r="I181" t="n">
-        <v>1.545454511957721</v>
+        <v>1.574074011525993</v>
       </c>
       <c r="J181" t="n">
         <v>-30</v>
@@ -9339,7 +9339,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -9594,7 +9594,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -9611,7 +9611,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -9621,14 +9621,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -9638,14 +9638,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -9679,7 +9679,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -9815,7 +9815,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -9832,7 +9832,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -9849,7 +9849,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Bellini Nautica S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -10036,7 +10036,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Bellini Nautica S.p.A.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -10053,7 +10053,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>E.P.H. S.p.A.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -10063,7 +10063,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -10172,7 +10172,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -10223,7 +10223,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>GPI S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -10240,7 +10240,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -10257,7 +10257,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -10274,7 +10274,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -10291,7 +10291,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ELSA Solutions S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -10308,7 +10308,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>ELSA Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -10335,7 +10335,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -10359,7 +10359,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>E.P.H. S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -10369,14 +10369,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -10386,14 +10386,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -10410,7 +10410,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -10427,7 +10427,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>Reway Group S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -10444,7 +10444,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -10461,7 +10461,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>STAR7 S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -10478,7 +10478,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Itway S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -10488,14 +10488,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -10512,7 +10512,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>Softlab S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -10522,14 +10522,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -10546,7 +10546,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -10563,7 +10563,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>STAR7 S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -10580,7 +10580,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -10597,7 +10597,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -10614,7 +10614,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -10631,7 +10631,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -10648,7 +10648,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>Itway S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -10658,14 +10658,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -10682,7 +10682,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -10699,7 +10699,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -10716,7 +10716,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10726,14 +10726,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10750,7 +10750,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>INNOVATEC S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10767,7 +10767,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10784,7 +10784,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10801,7 +10801,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>WEBSOLUTE S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10818,7 +10818,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>WEBSOLUTE S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10828,14 +10828,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10852,7 +10852,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10886,7 +10886,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>FRANCHETTI S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10903,7 +10903,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10913,14 +10913,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>GEL S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10937,7 +10937,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10954,7 +10954,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10971,7 +10971,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10988,7 +10988,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>Haiki+ S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10998,14 +10998,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11022,7 +11022,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>Somec S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11049,14 +11049,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11066,14 +11066,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Somec S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11083,14 +11083,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11107,7 +11107,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>TMP Group S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11117,14 +11117,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Softlab S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11134,14 +11134,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11158,7 +11158,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11175,7 +11175,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11192,7 +11192,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11209,7 +11209,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11226,7 +11226,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11243,7 +11243,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ESI S.p.A.</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11260,7 +11260,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11277,7 +11277,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11294,7 +11294,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11311,7 +11311,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11328,7 +11328,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11345,7 +11345,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Com.Tel S.p.A.</t>
+          <t>ESI S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11362,7 +11362,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11379,7 +11379,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11396,7 +11396,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11413,7 +11413,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11430,7 +11430,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11447,7 +11447,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>Com.Tel S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11464,7 +11464,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11474,14 +11474,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11491,14 +11491,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11508,14 +11508,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11532,7 +11532,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11549,7 +11549,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11559,14 +11559,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11576,14 +11576,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -11593,14 +11593,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -11610,14 +11610,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -11634,7 +11634,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -11651,7 +11651,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Haiki+ S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -11668,7 +11668,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -11685,7 +11685,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -11702,7 +11702,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>Emma Villas S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -11719,7 +11719,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -11736,7 +11736,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>GEL S.p.A.</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -11753,7 +11753,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -11770,7 +11770,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -11804,7 +11804,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11821,7 +11821,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11838,7 +11838,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11855,7 +11855,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11865,14 +11865,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11882,14 +11882,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11906,7 +11906,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11916,14 +11916,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11933,14 +11933,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11950,14 +11950,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11967,14 +11967,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11991,7 +11991,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -12025,7 +12025,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -12035,14 +12035,14 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -12052,14 +12052,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -12069,14 +12069,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -12086,14 +12086,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -12110,7 +12110,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -12127,7 +12127,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -12137,14 +12137,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -12161,7 +12161,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -12178,7 +12178,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12195,7 +12195,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12205,7 +12205,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -12229,7 +12229,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12239,14 +12239,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12256,7 +12256,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -12280,7 +12280,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12297,7 +12297,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12307,14 +12307,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12324,14 +12324,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12348,7 +12348,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12365,7 +12365,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>TECMA SOLUTIONS S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12382,7 +12382,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>TECMA SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12399,7 +12399,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12409,14 +12409,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12426,14 +12426,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12450,7 +12450,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12460,14 +12460,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -12477,7 +12477,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -12501,7 +12501,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -12511,14 +12511,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -12528,14 +12528,14 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -12552,7 +12552,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -12562,14 +12562,14 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -12586,7 +12586,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -12596,14 +12596,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -12613,7 +12613,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -12637,7 +12637,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -12654,7 +12654,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -12671,7 +12671,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -12681,14 +12681,14 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -12698,14 +12698,14 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -12715,14 +12715,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -12732,14 +12732,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -12749,14 +12749,14 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -12766,14 +12766,14 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -12790,7 +12790,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -12800,14 +12800,14 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -12817,14 +12817,14 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>TRAWELL CO S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -12834,14 +12834,14 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>TRAWELL CO S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -12851,14 +12851,14 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -12868,14 +12868,14 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -12892,7 +12892,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -12909,7 +12909,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -12926,7 +12926,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -12936,14 +12936,14 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -12960,7 +12960,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -12970,14 +12970,14 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -12994,7 +12994,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -13004,14 +13004,14 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -13028,7 +13028,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -13038,14 +13038,14 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -13055,14 +13055,14 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -13072,14 +13072,14 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -13089,14 +13089,14 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -13106,14 +13106,14 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -13130,7 +13130,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -13147,7 +13147,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -13157,14 +13157,14 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -13181,7 +13181,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -13198,7 +13198,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -13215,7 +13215,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -13225,14 +13225,14 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -13242,14 +13242,14 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -13259,14 +13259,14 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -13276,14 +13276,14 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -13293,14 +13293,14 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -13317,7 +13317,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -13327,14 +13327,14 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -13351,7 +13351,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -13361,14 +13361,14 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -13378,14 +13378,14 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -13395,14 +13395,14 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -13412,14 +13412,14 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -13436,7 +13436,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -13453,7 +13453,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -13470,7 +13470,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -13480,14 +13480,14 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -13497,14 +13497,14 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -13514,14 +13514,14 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -13531,14 +13531,14 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -13548,14 +13548,14 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -13572,7 +13572,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -13589,7 +13589,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -13606,7 +13606,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -13616,14 +13616,14 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -13633,14 +13633,14 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -13657,7 +13657,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -13674,7 +13674,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -13684,14 +13684,14 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -13708,7 +13708,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>Simone S.p.A.</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -13718,14 +13718,14 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -13735,14 +13735,14 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -13752,14 +13752,14 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -13776,7 +13776,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -13786,14 +13786,14 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -13810,7 +13810,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -13820,14 +13820,14 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -13837,14 +13837,14 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -13854,14 +13854,14 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Simone S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -13871,14 +13871,14 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -13895,7 +13895,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -13905,14 +13905,14 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -13929,7 +13929,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -13946,7 +13946,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -13963,7 +13963,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -13980,7 +13980,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -13997,7 +13997,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -14007,14 +14007,14 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -14031,7 +14031,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -14048,7 +14048,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -14065,7 +14065,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -14082,7 +14082,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>TENARIS S.A.</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -14092,14 +14092,14 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -14116,7 +14116,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -14126,14 +14126,14 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -14150,7 +14150,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -14167,7 +14167,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -14184,7 +14184,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>Confinvest Oro S.p.A.</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -14201,7 +14201,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -14211,14 +14211,14 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -14235,7 +14235,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -14252,7 +14252,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -14262,14 +14262,14 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -14279,14 +14279,14 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -14296,14 +14296,14 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -14313,14 +14313,14 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -14330,14 +14330,14 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -14347,7 +14347,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -14364,14 +14364,14 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -14381,14 +14381,14 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -14405,7 +14405,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -14415,14 +14415,14 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>TENARIS S.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -14439,7 +14439,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -14456,7 +14456,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -14473,7 +14473,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -14490,7 +14490,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Confinvest Oro S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -14500,14 +14500,14 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -14524,7 +14524,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -14534,14 +14534,14 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -14551,14 +14551,14 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -14575,7 +14575,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -14592,7 +14592,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -14602,14 +14602,14 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -14619,14 +14619,14 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -14636,14 +14636,14 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -14653,14 +14653,14 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -14670,14 +14670,14 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -14704,14 +14704,14 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -14728,7 +14728,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -14738,14 +14738,14 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>ESPE S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -14755,14 +14755,14 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -14779,7 +14779,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -14789,14 +14789,14 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -14813,7 +14813,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -14830,7 +14830,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -14840,14 +14840,14 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -14864,7 +14864,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -14874,14 +14874,14 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -14898,7 +14898,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -14915,7 +14915,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -14932,7 +14932,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -14942,14 +14942,14 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -14959,14 +14959,14 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>ESPE S.p.A.</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -14976,14 +14976,14 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -14993,14 +14993,14 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -15017,7 +15017,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -15034,7 +15034,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -15051,7 +15051,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -15068,7 +15068,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -15085,7 +15085,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -15102,7 +15102,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -15119,7 +15119,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -15136,7 +15136,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -15153,7 +15153,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -15163,14 +15163,14 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -15180,14 +15180,14 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -15197,14 +15197,14 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -15214,14 +15214,14 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -15231,14 +15231,14 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -15255,7 +15255,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -15272,7 +15272,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -15289,7 +15289,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -15306,7 +15306,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -15316,14 +15316,14 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -15333,14 +15333,14 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -15357,7 +15357,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -15367,14 +15367,14 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -15391,7 +15391,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -15408,7 +15408,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -15425,7 +15425,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -15435,14 +15435,14 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -15459,7 +15459,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -15469,14 +15469,14 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -15486,14 +15486,14 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -15503,14 +15503,14 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -15527,7 +15527,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -15537,14 +15537,14 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -15554,14 +15554,14 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -15571,14 +15571,14 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -15595,7 +15595,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -15605,14 +15605,14 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -15622,14 +15622,14 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -15646,7 +15646,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -15663,7 +15663,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -15680,7 +15680,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -15697,7 +15697,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -15714,7 +15714,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -15731,7 +15731,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -15741,14 +15741,14 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -15765,7 +15765,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -15775,14 +15775,14 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -15799,7 +15799,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -15809,14 +15809,14 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -15833,7 +15833,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -15843,14 +15843,14 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -15867,7 +15867,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -15877,14 +15877,14 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -15901,7 +15901,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -15918,7 +15918,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -15935,7 +15935,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -15952,7 +15952,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -15969,7 +15969,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -15986,7 +15986,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -15996,14 +15996,14 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -16020,7 +16020,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -16037,7 +16037,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -16054,7 +16054,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -16064,14 +16064,14 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>VINCENZO ZUCCHI S.p.A.</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -16081,14 +16081,14 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -16098,14 +16098,14 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -16115,14 +16115,14 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -16132,14 +16132,14 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -16190,7 +16190,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -16200,14 +16200,14 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -16217,14 +16217,14 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -16241,7 +16241,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -16258,7 +16258,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -16268,14 +16268,14 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -16285,14 +16285,14 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -16309,7 +16309,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>CLABO S.p.A.</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -16326,7 +16326,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>CLABO S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -16336,14 +16336,14 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>VINCENZO ZUCCHI S.p.A.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -16360,7 +16360,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -16370,14 +16370,14 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -16387,14 +16387,14 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -16404,14 +16404,14 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>BESTBE HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -16421,14 +16421,14 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -16445,7 +16445,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>BESTBE HOLDING S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -16455,14 +16455,14 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -16479,7 +16479,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -16530,7 +16530,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -16540,14 +16540,14 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -16557,14 +16557,14 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>DIADEMA CAPITAL</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -16581,7 +16581,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>DIADEMA CAPITAL</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -16591,14 +16591,14 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -16608,14 +16608,14 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -16625,14 +16625,14 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>IDNTT S.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -16642,14 +16642,14 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>EXPERT.AI S.p.A.</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -16659,14 +16659,14 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -16683,7 +16683,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>IDNTT S.A.</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -16700,7 +16700,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>EXPERT.AI S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -16710,14 +16710,14 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -16727,14 +16727,14 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -16785,7 +16785,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -16802,7 +16802,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -16812,7 +16812,7 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -16836,7 +16836,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -16846,14 +16846,14 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>Portobello S.p.A.</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -16863,14 +16863,14 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -16880,14 +16880,14 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>Portobello S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -16897,14 +16897,14 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -16914,7 +16914,7 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -16955,7 +16955,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>Vivenda Group S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -16965,14 +16965,14 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>MEVIM S.p.A.</t>
+          <t>COFLE S.p.A.</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -16989,7 +16989,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>COFLE S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -17006,7 +17006,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -17023,7 +17023,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>E-NOVIA S.p.A.</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -17057,7 +17057,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>Vivenda Group S.p.A.</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -17067,14 +17067,14 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>E-NOVIA S.p.A.</t>
+          <t>MEVIM S.p.A.</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -17091,7 +17091,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>ATON Green Storage S.p.A.</t>
+          <t>MONDO TV S.p.A.</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -17108,7 +17108,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>MONDO TV S.p.A.</t>
+          <t>ATON Green Storage S.p.A.</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -17125,7 +17125,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>Rocket Sharing Company S.p.A.</t>
+          <t>TALEA GROUP</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -17142,7 +17142,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>TALEA GROUP</t>
+          <t>Rocket Sharing Company S.p.A.</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -17159,7 +17159,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>Tenax International S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -17176,7 +17176,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -17186,14 +17186,14 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -17203,14 +17203,14 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -17220,14 +17220,14 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -17237,14 +17237,14 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>Tenax International S.p.A.</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -17254,14 +17254,14 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -17278,7 +17278,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -17295,7 +17295,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>Cube Labs S.p.A.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -17312,7 +17312,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -17329,7 +17329,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>Cube Labs S.p.A.</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -17346,7 +17346,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -17356,14 +17356,14 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -17373,14 +17373,14 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>Otofarma S.p.A.</t>
+          <t>Piu' Medical S.p.A.</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -17414,7 +17414,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>Otofarma S.p.A.</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -17424,14 +17424,14 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -17441,14 +17441,14 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -17458,14 +17458,14 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>Piu' Medical S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -17475,14 +17475,14 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -17492,14 +17492,14 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>Cloudia Research S.p.A.</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -17516,7 +17516,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>Cloudia Research S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -17533,7 +17533,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>H-FARM S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -17543,14 +17543,14 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>Adventure S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -17567,7 +17567,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>Finanza.tech S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -17577,14 +17577,14 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>TMP Group S.p.A.</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -17601,7 +17601,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>OVS S.p.A.</t>
+          <t>H-FARM S.p.A.</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -17611,14 +17611,14 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>OVS S.p.A.</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -17635,7 +17635,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>Triboo S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -17652,7 +17652,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -17669,7 +17669,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>Triboo S.p.A.</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -17686,7 +17686,7 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -17696,14 +17696,14 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>Adventure S.p.A.</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -17728,104 +17728,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>stock_name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>detachment_date</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>payment_date</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>last_close</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dividend</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>miss_days</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>is_opportunity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Italian Wine Brands S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IT0005075764</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-05-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>19.89999961853027</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>2.512562862234506</v>
-      </c>
-      <c r="I2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17836,316 +17741,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ACEA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Adventure S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>CULTI Milano S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Cloudia Research S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>E-Globe S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>ECOSUNTEK S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Gentili Mosconi S.p.A.</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>H-FARM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>OPS ECOM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>OVS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>TMP Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Triboo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Vantea Smart S.p.A.</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>